--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920357</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>129920365</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129920364</v>
       </c>
       <c r="B4" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129920358</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>129920365</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129920364</v>
       </c>
       <c r="B4" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920357</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>129920365</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129920364</v>
       </c>
       <c r="B4" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129920358</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>129920364</v>
       </c>
       <c r="B4" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>129920364</v>
       </c>
       <c r="B4" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920357</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>129920365</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129920364</v>
       </c>
       <c r="B4" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129920358</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920357</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>129920365</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129920364</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129920356</v>
       </c>
       <c r="B5" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129920358</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55597-2025 artfynd.xlsx
+++ b/artfynd/A 55597-2025 artfynd.xlsx
@@ -1179,7 +1179,7 @@
         <v>131118183</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
